--- a/신고신저가_20260730.xlsx
+++ b/신고신저가_20260730.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,16 +77,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -454,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -612,7 +617,42 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: AI 하드웨어 체인(반도체·PCB·데이터센터 전력) 글로벌 동반 조정, 자금은 자동차·은행·헬스케어·소비 등 저PBR·고배당 가치주로 로테이션. 트리거는 피치의 AI 대규모 투자 신용리스크 경고 + SK하이닉스 실적 미달 + 한국증시 급락 성격.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美: 다우 -2.19%·나스닥 -1.74%·S&amp;P -1.52%로 지수는 하락했으나 신고가 124&gt;신저가 69. 강세 금융(순강도+34, 중앙 PER 18.3)·테크서비스(+21)·헬스(+14), 약세 전자기술(-28, 신저 32)·산업재(XLI -3.2%). 실적 서프라이즈 MANH +21%·GRMN +16%·GEHC +12% 신고, 반면 HVAC 쇼크로 LII -21%가 WSO -13% 동반, 데이터센터 전력 VRT -17%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日: 신고47/신저20. 자동차·기계 급등(자동차ETF +5.6%) — 토요타 +7%·스바루 +6%·코마츠 +8%·시마노 +10%·코나미 +13%, 저PBR 로테이션. 반면 반도체 붕괴 — 코쿠사이 -18%·이비덴 -9%·르네사스·레이저테크 -8%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 中·홍콩: 지수는 상승(항셍 +1.96%·항셍테크 +2.84%·상해종합 +0.40%·CSI300 +0.67%)했으나 내부 차별화. 홍콩(신고24/신저8) 금융·카지노·인터넷 강세(스탠다드차타드·은하오락·텐센트뮤직), 신저는 반도체·PCB(SMIC·몽타주·성훙테크). 中(신고12/신저27)은 은행(순강도+6)·거리전기 등 고배당·소비 신고, 반면 전자기술 -14(신저14)로 CPO·PCB·반도체 집중 하락(둥산징미·신위안·중차이커지), 과창50 -4%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ① 피치 AI자본지출 신용우려·SK하이닉스 실적이 촉발한 반도체 조정 → 8월 초 美 빅테크·엔비디아 실적으로 재평가 여부 ② HVAC(LII/WSO) 실적쇼크의 주택·경기소비 파급 ③ 中 은행·소비 고배당 로테이션 지속성 vs 성장주 반등 시점</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -710,19 +750,19 @@
       <c r="C2" t="n">
         <v>7316.15</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-1.52</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>-1.67</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>2.48</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>6.88</v>
       </c>
       <c r="I2" t="n">
@@ -748,19 +788,19 @@
       <c r="C3" t="n">
         <v>24442.94</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-1.74</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>-4.86</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>-5.33</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>5.17</v>
       </c>
       <c r="I3" t="n">
@@ -786,19 +826,19 @@
       <c r="C4" t="n">
         <v>6023.66</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>-10.84</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>-10.73</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-28.39</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-6.98</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>42.94</v>
       </c>
       <c r="I4" t="n">
@@ -824,19 +864,19 @@
       <c r="C5" t="n">
         <v>62364.92</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>-3.95</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>-5.84</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>-10.09</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>5.45</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>23.89</v>
       </c>
       <c r="I5" t="n">
@@ -860,11 +900,11 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -880,11 +920,11 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
@@ -900,11 +940,11 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
     </row>
@@ -920,11 +960,11 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
     </row>
@@ -1023,7 +1063,7 @@
       <c r="F2" t="n">
         <v>34</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1058,7 +1098,7 @@
       <c r="F3" t="n">
         <v>21</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1093,7 +1133,7 @@
       <c r="F4" t="n">
         <v>14</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1128,7 +1168,7 @@
       <c r="F5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1163,7 +1203,7 @@
       <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1198,7 +1238,7 @@
       <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1233,7 +1273,7 @@
       <c r="F8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1268,7 +1308,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1303,7 +1343,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1338,7 +1378,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1373,7 +1413,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1408,7 +1448,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1443,7 +1483,7 @@
       <c r="F14" t="n">
         <v>-1</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1478,7 +1518,7 @@
       <c r="F15" t="n">
         <v>-2</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1513,7 +1553,7 @@
       <c r="F16" t="n">
         <v>-6</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1548,7 +1588,7 @@
       <c r="F17" t="n">
         <v>-10</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1583,7 +1623,7 @@
       <c r="F18" t="n">
         <v>-28</v>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1723,7 +1763,7 @@
       <c r="F22" t="n">
         <v>8</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1758,7 +1798,7 @@
       <c r="F23" t="n">
         <v>7</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1793,7 +1833,7 @@
       <c r="F24" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1828,7 +1868,7 @@
       <c r="F25" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1863,7 +1903,7 @@
       <c r="F26" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1898,7 +1938,7 @@
       <c r="F27" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1933,7 +1973,7 @@
       <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1968,7 +2008,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2003,7 +2043,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2038,7 +2078,7 @@
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2073,7 +2113,7 @@
       <c r="F32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2108,7 +2148,7 @@
       <c r="F33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2143,7 +2183,7 @@
       <c r="F34" t="n">
         <v>-1</v>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2178,7 +2218,7 @@
       <c r="F35" t="n">
         <v>-1</v>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2213,7 +2253,7 @@
       <c r="F36" t="n">
         <v>-3</v>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2248,7 +2288,7 @@
       <c r="F37" t="n">
         <v>-7</v>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2353,7 +2393,7 @@
       <c r="F40" t="n">
         <v>9</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2388,7 +2428,7 @@
       <c r="F41" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2423,7 +2463,7 @@
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2458,7 +2498,7 @@
       <c r="F43" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2493,7 +2533,7 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2528,7 +2568,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2563,7 +2603,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2598,7 +2638,7 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2633,7 +2673,7 @@
       <c r="F48" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2668,7 +2708,7 @@
       <c r="F49" t="n">
         <v>-3</v>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2703,7 +2743,7 @@
       <c r="F50" t="n">
         <v>-5</v>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2983,7 +3023,7 @@
       <c r="F58" t="n">
         <v>6</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3018,7 +3058,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3053,7 +3093,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3088,7 +3128,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3123,7 +3163,7 @@
       <c r="F62" t="n">
         <v>-1</v>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3156,7 +3196,7 @@
       <c r="F63" t="n">
         <v>-1</v>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3191,7 +3231,7 @@
       <c r="F64" t="n">
         <v>-1</v>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3226,7 +3266,7 @@
       <c r="F65" t="n">
         <v>-1</v>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3261,7 +3301,7 @@
       <c r="F66" t="n">
         <v>-7</v>
       </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3296,7 +3336,7 @@
       <c r="F67" t="n">
         <v>-14</v>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3605,30 +3645,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3649,90 +3690,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -3754,58 +3800,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>1D -2.6%(1M -10.2%). 전자기술 순강도 -28·신저 32로 최약, AI반도체 체인 조정 직격</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
         <v>-2.6</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="F2" s="10" t="n">
         <v>-7.6</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" s="10" t="n">
         <v>-10.2</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="H2" s="10" t="n">
         <v>5.7</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="I2" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="K2" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="M2" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="O2" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="7" t="n">
+      <c r="Q2" s="10" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="7" t="n">
+      <c r="S2" s="10" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="7" t="n">
+      <c r="U2" s="10" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3825,58 +3876,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>1D -0.6%로 방어. 헬스테크 순강도 +14 강세, GEHC 신고 등 실적 로테이션 수혜</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F3" s="10" t="n">
         <v>4.3</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="G3" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="H3" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="I3" s="10" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="K3" s="10" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="O3" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="Q3" s="10" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="7" t="n">
+      <c r="S3" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="7" t="n">
+      <c r="U3" s="10" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3896,58 +3952,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>1D -1.6%지만 금융 순강도 +34(신고 36)로 섹터 최강, 저PER 18.3 가치 매수 지속</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="F4" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="10" t="n">
         <v>5.5</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="H4" s="10" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="I4" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="K4" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="M4" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="O4" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="Q4" s="10" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="7" t="n">
+      <c r="S4" s="10" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="7" t="n">
+      <c r="U4" s="10" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3967,58 +4028,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>1D -0.8%. 소매·내구소비 신고 6·2로 견조하나 지수 조정에 소폭 약세</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="F5" s="10" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="G5" s="10" t="n">
         <v>-4.7</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="H5" s="10" t="n">
         <v>-4.4</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="I5" s="10" t="n">
         <v>-6.2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="K5" s="10" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="O5" s="10" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="Q5" s="10" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="7" t="n">
+      <c r="S5" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="7" t="n">
+      <c r="U5" s="10" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4038,58 +4104,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>1D -0.1%로 보합. 커뮤니케이션 순강도 -2 혼조, 대형주 방향성 부재</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="F6" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="10" t="n">
         <v>-5.1</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="I6" s="10" t="n">
         <v>-6.4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="K6" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="10" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="O6" s="10" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="Q6" s="10" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="S6" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="7" t="n">
+      <c r="U6" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4109,58 +4180,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>1D -3.2%로 SPDR 최약. 생산재 순강도 -10(신저14), 산업서비스 -6 동반 부진</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>-3.2</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="F7" s="10" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="G7" s="10" t="n">
         <v>-3.3</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="H7" s="10" t="n">
         <v>3.6</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="I7" s="10" t="n">
         <v>14.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="K7" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="10" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="O7" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="Q7" s="10" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="7" t="n">
+      <c r="S7" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="U7" s="10" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4180,58 +4256,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>1D +0.3%로 유일 소폭 상승권. 필수소비 순강도 +6, 방어 로테이션 수혜</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="I8" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="K8" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="M8" s="10" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="O8" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="Q8" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="S8" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="U8" s="10" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4251,58 +4332,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>1D +1.9%로 최강. 유가 강세, YTD +33% 섹터 1위 유지</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="F9" s="10" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="10" t="n">
         <v>9.5</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="H9" s="10" t="n">
         <v>2.4</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="I9" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="K9" s="10" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="M9" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="O9" s="10" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="7" t="n">
+      <c r="Q9" s="10" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="7" t="n">
+      <c r="S9" s="10" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="7" t="n">
+      <c r="U9" s="10" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4322,58 +4408,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>1D -1.3%. 유틸 순강도 혼조, 금리·성장주 조정 여파로 동반 약세</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="F10" s="10" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="10" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="H10" s="10" t="n">
         <v>-2.3</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="I10" s="10" t="n">
         <v>6.6</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="K10" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="O10" s="10" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="Q10" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="S10" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="U10" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4393,58 +4484,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>1D -1.1%. 소재 순강도 -1, 비에너지광물 신저 등 경기민감 약세</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="F11" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="H11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="I11" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="K11" s="10" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="M11" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="O11" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="Q11" s="10" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="7" t="n">
+      <c r="S11" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="U11" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4464,58 +4560,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>1D -0.1%로 견조. BXP 오피스 리츠 실적 서프라이즈 신고, 금리 민감 완화</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="F12" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="G12" s="10" t="n">
         <v>2.3</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="H12" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="I12" s="10" t="n">
         <v>15.7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="K12" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="M12" s="10" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="O12" s="10" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="Q12" s="10" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="S12" s="10" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="U12" s="10" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4535,58 +4636,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="10" t="n">
         <v>2.3</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="F13" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="G13" s="10" t="n">
         <v>4.9</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="H13" s="10" t="n">
         <v>13.4</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="I13" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="K13" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="M13" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="O13" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="Q13" s="10" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="7" t="n">
+      <c r="S13" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="U13" s="10" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4606,58 +4708,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="F14" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="10" t="n">
         <v>9.1</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="H14" s="10" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="I14" s="10" t="n">
         <v>16.5</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="K14" s="10" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="M14" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="O14" s="10" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="Q14" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="S14" s="10" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="U14" s="10" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4677,58 +4780,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="10" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="F15" s="10" t="n">
         <v>-2.9</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="10" t="n">
         <v>-7.6</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="10" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="I15" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>13</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="K15" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="M15" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="O15" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="Q15" s="10" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="S15" s="10" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="U15" s="10" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4748,58 +4852,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="F16" s="10" t="n">
         <v>-4.7</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="G16" s="10" t="n">
         <v>-4.3</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="H16" s="10" t="n">
         <v>4.6</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="I16" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="K16" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="M16" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="O16" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="Q16" s="10" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="S16" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="U16" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4819,58 +4924,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="F17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="H17" s="10" t="n">
         <v>2.3</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="I17" s="10" t="n">
         <v>6.9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="K17" s="10" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="M17" s="10" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="O17" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="Q17" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="7" t="n">
+      <c r="S17" s="10" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="U17" s="10" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4890,58 +4996,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="F18" s="10" t="n">
         <v>9.5</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="G18" s="10" t="n">
         <v>14.8</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="H18" s="10" t="n">
         <v>11.1</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="I18" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="K18" s="10" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="M18" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="O18" s="10" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="Q18" s="10" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="S18" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="U18" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4961,58 +5068,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="10" t="n">
         <v>-3.6</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="F19" s="10" t="n">
         <v>-10.3</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="G19" s="10" t="n">
         <v>-20.8</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="H19" s="10" t="n">
         <v>-21.3</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="I19" s="10" t="n">
         <v>25.6</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>3</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="K19" s="10" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="M19" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="O19" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="Q19" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="7" t="n">
+      <c r="S19" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="7" t="n">
+      <c r="U19" s="10" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5032,58 +5140,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="10" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="F20" s="10" t="n">
         <v>-4.6</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="G20" s="10" t="n">
         <v>-6.1</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="H20" s="10" t="n">
         <v>-7.5</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="I20" s="10" t="n">
         <v>14.4</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="K20" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="M20" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="O20" s="10" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="Q20" s="10" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="S20" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="U20" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5103,58 +5212,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="10" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="F21" s="10" t="n">
         <v>-8.6</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="G21" s="10" t="n">
         <v>-14.9</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="H21" s="10" t="n">
         <v>4.5</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="I21" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>5</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="K21" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="M21" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="O21" s="10" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="Q21" s="10" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="7" t="n">
+      <c r="S21" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="7" t="n">
+      <c r="U21" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5174,58 +5284,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="F22" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="G22" s="10" t="n">
         <v>7.3</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="H22" s="10" t="n">
         <v>11.6</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="I22" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>12</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="K22" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="M22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="O22" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="Q22" s="10" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="7" t="n">
+      <c r="S22" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="7" t="n">
+      <c r="U22" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5245,58 +5356,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="F23" s="10" t="n">
         <v>2.4</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="H23" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="I23" s="10" t="n">
         <v>4.3</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="K23" s="10" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="M23" s="10" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="O23" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="Q23" s="10" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="7" t="n">
+      <c r="S23" s="10" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="7" t="n">
+      <c r="U23" s="10" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5316,58 +5428,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="F24" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="G24" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="H24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="I24" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>10</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="K24" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="M24" s="10" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="O24" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="Q24" s="10" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="S24" s="10" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="7" t="n">
+      <c r="U24" s="10" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5387,58 +5500,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="F25" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="G25" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="H25" s="10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="I25" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="K25" s="10" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="M25" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="O25" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="Q25" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="7" t="n">
+      <c r="S25" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="7" t="n">
+      <c r="U25" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5458,58 +5572,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="F26" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="G26" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="H26" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="I26" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>10</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="K26" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="M26" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="O26" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="Q26" s="10" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="7" t="n">
+      <c r="S26" s="10" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="7" t="n">
+      <c r="U26" s="10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5529,58 +5644,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="10" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="F27" s="10" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="G27" s="10" t="n">
         <v>9.4</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="H27" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="I27" s="10" t="n">
         <v>45.6</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="K27" s="10" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="M27" s="10" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="O27" s="10" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="Q27" s="10" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="7" t="n">
+      <c r="S27" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="7" t="n">
+      <c r="U27" s="10" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5600,58 +5716,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="F28" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="G28" s="10" t="n">
         <v>13.2</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="H28" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="I28" s="10" t="n">
         <v>34.5</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="K28" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="M28" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="O28" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="Q28" s="10" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="7" t="n">
+      <c r="S28" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="7" t="n">
+      <c r="U28" s="10" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5671,58 +5788,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="F29" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="G29" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="H29" s="10" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="I29" s="10" t="n">
         <v>2.4</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="K29" s="10" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="M29" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="O29" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="Q29" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="7" t="n">
+      <c r="S29" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="7" t="n">
+      <c r="U29" s="10" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5742,58 +5860,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="F30" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="G30" s="10" t="n">
         <v>12.3</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="H30" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="I30" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="K30" s="10" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="M30" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="7" t="n">
+      <c r="O30" s="10" t="n">
         <v>-11.9</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="7" t="n">
+      <c r="Q30" s="10" t="n">
         <v>-14.4</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="7" t="n">
+      <c r="S30" s="10" t="n">
         <v>-13.5</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="7" t="n">
+      <c r="U30" s="10" t="n">
         <v>-1.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5813,58 +5932,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="10" t="n">
         <v>2.2</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="F31" s="10" t="n">
         <v>4.6</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="G31" s="10" t="n">
         <v>14.1</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="H31" s="10" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="I31" s="10" t="n">
         <v>-1.9</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="7" t="n">
+      <c r="K31" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="M31" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="7" t="n">
+      <c r="O31" s="10" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="7" t="n">
+      <c r="Q31" s="10" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="7" t="n">
+      <c r="S31" s="10" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="7" t="n">
+      <c r="U31" s="10" t="n">
         <v>-2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5884,56 +6004,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="10" t="n">
         <v>2.7</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="F32" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="G32" s="10" t="n">
         <v>10.7</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="H32" s="10" t="n">
         <v>-1.3</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="I32" s="10" t="n">
         <v>-11.5</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="K32" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="M32" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="7" t="n">
+      <c r="O32" s="10" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="7" t="n">
+      <c r="Q32" s="10" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="7" t="n">
+      <c r="S32" s="10" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="7" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="10" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5951,24 +6072,29 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" s="7" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" s="7" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" s="7" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 전자기술 순강도 -14·신저 14로 섹터 최약, CPO·PCB·반도체 집중 하락 추정</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" s="10" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" s="10" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" s="10" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5986,24 +6112,29 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" s="7" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" s="7" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" s="7" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 테크서비스 순강도 -1, 과창50 -4% 여파 약세 추정</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr"/>
+      <c r="H34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" s="10" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="10" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" s="10" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" s="10" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" s="10" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6021,24 +6152,29 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" s="7" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" s="7" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" s="7" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 통신 순강도 0 중립 추정</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="10" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" s="10" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" s="10" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" s="10" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6056,56 +6192,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>1D +1.7%. 신에너지차 반등하나 1M -13.2%·3M -22.7%로 중기 약세 지속</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="F36" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="G36" s="10" t="n">
         <v>-13.2</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="H36" s="10" t="n">
         <v>-22.7</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="I36" s="10" t="n">
         <v>-14.2</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="J36" s="7" t="n">
+      <c r="K36" s="10" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>2</v>
       </c>
-      <c r="L36" s="7" t="n">
+      <c r="M36" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>2</v>
       </c>
-      <c r="N36" s="7" t="n">
+      <c r="O36" s="10" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2</v>
       </c>
-      <c r="P36" s="7" t="n">
+      <c r="Q36" s="10" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>3</v>
       </c>
-      <c r="R36" s="7" t="n">
+      <c r="S36" s="10" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="7" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="10" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6123,24 +6264,29 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" s="7" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" s="7" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" s="7" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 방산 관련 신고/신저 특이신호 미미, 중립 추정</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="10" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr"/>
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" s="10" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" s="10" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6158,56 +6304,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>1D +0.4%. 태양광 소폭 반등하나 1M -21.7%·3M -22.5%로 중기 최약</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="F38" s="10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="G38" s="10" t="n">
         <v>-21.7</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="H38" s="10" t="n">
         <v>-22.5</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="I38" s="10" t="n">
         <v>-15.2</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>3</v>
       </c>
-      <c r="J38" s="7" t="n">
+      <c r="K38" s="10" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>3</v>
       </c>
-      <c r="L38" s="7" t="n">
+      <c r="M38" s="10" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3</v>
       </c>
-      <c r="N38" s="7" t="n">
+      <c r="O38" s="10" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>3</v>
       </c>
-      <c r="P38" s="7" t="n">
+      <c r="Q38" s="10" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>1</v>
       </c>
-      <c r="R38" s="7" t="n">
+      <c r="S38" s="10" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="7" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="10" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6225,24 +6376,29 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr"/>
-      <c r="F39" s="7" t="inlineStr"/>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" s="7" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" s="7" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" s="7" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 백주 순강도 특이신호 없음, 중립 추정</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="10" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr"/>
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" s="10" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" s="10" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" s="10" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6260,24 +6416,29 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" s="7" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" s="7" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" s="7" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 금융 순강도 +6(은행 신고), 고배당 로테이션 최강 추정</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr"/>
+      <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" s="10" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="10" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" s="10" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" s="10" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" s="10" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6295,58 +6456,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>1D +1.8%. 유색금속 반등하나 3M -15.6%, 비에너지광물 신저로 중기 부진</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="F41" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="G41" s="10" t="n">
         <v>-4.6</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="H41" s="10" t="n">
         <v>-15.6</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="I41" s="10" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="7" t="n">
+      <c r="K41" s="10" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="7" t="n">
+      <c r="M41" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="7" t="n">
+      <c r="O41" s="10" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="P41" s="7" t="n">
+      <c r="Q41" s="10" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>2</v>
       </c>
-      <c r="R41" s="7" t="n">
+      <c r="S41" s="10" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="7" t="n">
+      <c r="U41" s="10" t="n">
         <v>41.8</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6366,24 +6532,29 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" s="7" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" s="7" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" s="7" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 부동산 특이신호 미미, 중립 추정</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr"/>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" s="10" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="10" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" s="10" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" s="10" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" s="10" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6401,24 +6572,29 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" s="7" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" s="7" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" s="7" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 증권은 금융 순강도 +6 온기에 상대 견조 추정</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="10" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr"/>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="10" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" s="10" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" s="10" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" s="10" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6436,24 +6612,29 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" s="7" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" s="7" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" s="7" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" s="7" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 의약 순강도 0 중립 추정</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" s="10" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="10" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" s="10" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" s="10" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" s="10" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6471,24 +6652,29 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr"/>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" s="7" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" s="7" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" s="7" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" s="7" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 소비 순강도 +2(거리전기 신고), 대소비재 역방향 강세 추정</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="10" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr"/>
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="10" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" s="10" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" s="10" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" s="10" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6498,7 +6684,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3.6"/>
@@ -6510,7 +6696,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-10.3"/>
@@ -6522,7 +6708,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-21.7"/>
@@ -6534,7 +6720,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-22.7"/>
@@ -6546,7 +6732,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-15.2"/>
@@ -6558,7 +6744,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -6568,7 +6754,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -6580,7 +6766,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -6592,7 +6778,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.6"/>
@@ -6604,7 +6790,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -6616,7 +6802,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -6724,12 +6910,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6774,15 +6960,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>레녹스인터내셔널(주거용 HVAC): 2Q매출 소폭 미달·FY EPS가이던스 $23.50으로 하향(컨센 -4.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6823,15 +7013,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>아이렌(비트코인채굴·AI데이터센터): AI랠리 차익실현+섹터 광범위 매도·창업자 보상 희석 우려</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6876,15 +7070,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>왓스코(HVAC유통): 2Q EPS $4.00 컨센 $4.39 미달·매출총이익률 27.5%로 전년比 축소</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6929,15 +7127,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>왓스코 B주(HVAC유통): 2Q EPS $4.00 컨센 미달·마진 축소, 보통주와 동반 급락</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6978,15 +7180,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>에버코어(독립자문 투자은행): 2Q EPS 소폭 상회했으나 1Q 역대최고 대비 실망·'뉴스에 팔자'</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7027,15 +7233,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7080,15 +7286,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7129,15 +7335,15 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7178,15 +7384,15 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7227,15 +7433,15 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7276,15 +7482,15 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7325,15 +7531,15 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7374,15 +7580,15 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7423,15 +7629,15 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7470,15 +7676,15 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7521,15 +7727,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7570,15 +7776,15 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="M18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7619,15 +7825,15 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7668,15 +7874,15 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7717,15 +7923,15 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7766,15 +7972,15 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="M22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7815,15 +8021,15 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7862,15 +8068,15 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr"/>
+      <c r="M24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7909,15 +8115,15 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7958,15 +8164,15 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8007,15 +8213,15 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8058,15 +8264,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8107,15 +8313,15 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8156,10 +8362,10 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8205,10 +8411,14 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>버티브(데이터센터 전력·냉각): 2Q매출 $3.27B 컨센 $3.38B 미달·공급망 타이밍 이슈로 급락</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8256,10 +8466,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>이니오(산업용 엔진·에너지솔루션): 2Q매출 +42% 상회했으나 마진 우려로 실적발표 후 급락</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8305,10 +8519,14 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>온투이노베이션(반도체 계측장비): 8/6 실적발표 앞두고 반도체장비 섹터 전반 매도·중국경쟁 우려</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8356,10 +8574,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8405,14 +8623,14 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="M35" s="11" t="inlineStr">
         <is>
           <t>(전일) (반도체 소재·CMP): 섹터 약세 속 AI칩 지출 둔화 우려로 낙폭 지속</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8458,14 +8676,14 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="M36" s="11" t="inlineStr">
         <is>
           <t>(전일) (반도체 계측장비): 개별 뉴스 없음, SMH -3% 섹터 약세 동반 하락(수급)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8511,14 +8729,14 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="M37" s="11" t="inlineStr">
         <is>
           <t>(전일) (광통신 부품·레이저): 코닝 가이던스 쇼크발 광통신 섹터 연쇄 하락, AI투자 ROI 우려</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8562,10 +8780,10 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8611,10 +8829,10 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8660,10 +8878,10 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8709,10 +8927,10 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8758,10 +8976,10 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="9" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8807,14 +9025,14 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="M43" s="11" t="inlineStr">
         <is>
           <t>(전일) (파운드리·아날로그 반도체): 코닝 쇼크 촉발 AI 인프라 섹터 급매도 동반 하락(실적 8/4)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8860,10 +9078,10 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8909,10 +9127,10 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="9" t="inlineStr"/>
+      <c r="M45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8958,10 +9176,10 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9007,10 +9225,10 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9056,14 +9274,14 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr">
+      <c r="M48" s="11" t="inlineStr">
         <is>
           <t>(전일) (반도체 패키징 OSAT): 2Q 실적 비트에도 3Q 매출 가이던스 컨센 -4% 하회로 -25% 급락</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9109,14 +9327,14 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="9" t="inlineStr">
+      <c r="M49" s="11" t="inlineStr">
         <is>
           <t>(전일) (인쇄회로기판 PCB): 전자부품 제조 섹터 광범위 매물 출회, 섹터 수급 악화로 신저가</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9162,10 +9380,10 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9209,14 +9427,14 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="9" t="inlineStr">
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>(전일) (반도체 타이밍칩): 반도체 섹터(SMH -3%) AI칩 밸류 우려 매도세</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9262,10 +9480,10 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9311,10 +9529,10 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="9" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9360,10 +9578,10 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9407,10 +9625,10 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="9" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9456,10 +9674,10 @@
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" s="9" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9503,10 +9721,10 @@
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="9" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9554,10 +9772,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M58" s="9" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9603,10 +9821,10 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="9" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9652,10 +9870,10 @@
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="9" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9701,10 +9919,10 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9750,14 +9968,14 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" s="9" t="inlineStr">
+      <c r="M62" s="11" t="inlineStr">
         <is>
           <t>(전일) (반도체 파운드리): 내부자 주식매도 공시·고평가 논란 속 반도체 조정 연장</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9803,10 +10021,10 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9856,10 +10074,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M64" s="9" t="inlineStr"/>
+      <c r="M64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9905,10 +10123,10 @@
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="9" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9954,10 +10172,10 @@
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
+      <c r="M66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10001,10 +10219,10 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" s="9" t="inlineStr"/>
+      <c r="M67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10050,14 +10268,14 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
+      <c r="M68" s="11" t="inlineStr">
         <is>
           <t>(전일) (연료전지 분산발전): 숏셀러 공급망 의혹·데이터센터 프로젝트 지연 우려로 약세, 실적 전 하락</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10105,10 +10323,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M69" s="9" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10154,19 +10372,19 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" s="9" t="inlineStr">
+      <c r="M70" s="11" t="inlineStr">
         <is>
           <t>(전일) (유전서비스): 실적 상회에도 에너지 섹터 약세·유가 불확실성으로 하락</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10207,15 +10425,19 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" s="9" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>맨해튼어소시에이츠(공급망·WMS 소프트웨어): 2Q 클라우드매출 +26%·EPS 6%상회·연간가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10256,15 +10478,19 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr"/>
+      <c r="M72" s="11" t="inlineStr">
+        <is>
+          <t>GE헬스케어(의료영상·진단장비): 2Q매출 53억달러·EPS 8%상회·수주 +11%·연간가이던스 재확인</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10309,15 +10535,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M73" s="9" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>클린하버스(산업폐기물 처리): 2Q매출 +12%·EBITDA마진 역대최고 23.6%·6억달러 10년 신규계약</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10360,15 +10590,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M74" s="9" t="inlineStr"/>
+      <c r="M74" s="11" t="inlineStr">
+        <is>
+          <t>스노우플레이크(클라우드 데이터플랫폼): 웰스파고 목표가 $320→$500 상향·AI에이전트 지출 가속 논거</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10409,15 +10643,19 @@
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" s="9" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>BXP(오피스 리츠): 2Q FFO $1.78 예상상회·연간FFO가이던스 상향·매출 +3.1%</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10462,15 +10700,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M76" s="9" t="inlineStr"/>
+      <c r="M76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10511,15 +10749,15 @@
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10558,15 +10796,15 @@
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" s="9" t="inlineStr"/>
+      <c r="M78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10607,15 +10845,15 @@
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" s="9" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10660,15 +10898,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M80" s="9" t="inlineStr"/>
+      <c r="M80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10709,15 +10947,15 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" s="9" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10758,15 +10996,15 @@
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" s="9" t="inlineStr"/>
+      <c r="M82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10807,15 +11045,15 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" s="9" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10856,15 +11094,15 @@
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" s="9" t="inlineStr"/>
+      <c r="M84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10905,15 +11143,15 @@
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" s="9" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10958,15 +11196,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M86" s="9" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11011,15 +11249,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M87" s="9" t="inlineStr"/>
+      <c r="M87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11064,15 +11302,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M88" s="9" t="inlineStr"/>
+      <c r="M88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11113,15 +11351,15 @@
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" s="9" t="inlineStr"/>
+      <c r="M89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11162,15 +11400,15 @@
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" s="9" t="inlineStr"/>
+      <c r="M90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11211,15 +11449,15 @@
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" s="9" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11264,15 +11502,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M92" s="9" t="inlineStr"/>
+      <c r="M92" s="11" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11317,15 +11555,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M93" s="9" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11370,15 +11608,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M94" s="9" t="inlineStr"/>
+      <c r="M94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11423,15 +11661,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M95" s="9" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11472,15 +11710,15 @@
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" s="9" t="inlineStr"/>
+      <c r="M96" s="11" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11521,15 +11759,15 @@
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" s="9" t="inlineStr"/>
+      <c r="M97" s="11" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11574,10 +11812,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M98" s="9" t="inlineStr"/>
+      <c r="M98" s="11" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11627,10 +11865,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M99" s="9" t="inlineStr"/>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>가민(GPS·웨어러블기기): 2Q매출 $2.02B 상회·피트니스 +25%·FY EPS가이던스 $10.00으로 상향</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11676,14 +11918,14 @@
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" s="9" t="inlineStr">
+      <c r="M100" s="11" t="inlineStr">
         <is>
           <t>(전일) (HR·재무 SaaS): AI 에이전트 모멘텀·저평가 부각, 소프트웨어 섹터 반등 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11729,10 +11971,10 @@
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
-      <c r="M101" s="9" t="inlineStr"/>
+      <c r="M101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11778,10 +12020,10 @@
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
-      <c r="M102" s="9" t="inlineStr"/>
+      <c r="M102" s="11" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11827,10 +12069,10 @@
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
-      <c r="M103" s="9" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11876,10 +12118,10 @@
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" s="9" t="inlineStr"/>
+      <c r="M104" s="11" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11925,10 +12167,10 @@
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
-      <c r="M105" s="9" t="inlineStr"/>
+      <c r="M105" s="11" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11974,10 +12216,10 @@
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" s="9" t="inlineStr"/>
+      <c r="M106" s="11" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12027,14 +12269,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M107" s="9" t="inlineStr">
-        <is>
-          <t>(전일) (온라인여행플랫폼): 얼리전트항공과 독점 OTA 파트너십(566개 노선) 체결로 급등</t>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>익스피디아(온라인여행플랫폼): 제프리스 목표가 상향·알리전트항공 독점파트너십·실적기대 선반영</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12084,14 +12326,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M108" s="9" t="inlineStr">
+      <c r="M108" s="11" t="inlineStr">
         <is>
           <t>(전일) (위성라디오): 분기배당 $0.27 선언·2Q 이익 개선 기대 선반영</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12137,10 +12379,10 @@
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12184,10 +12426,10 @@
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" s="9" t="inlineStr"/>
+      <c r="M110" s="11" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12237,10 +12479,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M111" s="9" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>솔벤텀(의료기기·헬스IT): UBS 투자의견 중립→매수 상향·8/5 실적발표 앞두고 애널리스트 낙관</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12286,10 +12532,10 @@
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
-      <c r="M112" s="9" t="inlineStr"/>
+      <c r="M112" s="11" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12333,10 +12579,10 @@
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" s="9" t="inlineStr"/>
+      <c r="M113" s="11" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12384,14 +12630,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M114" s="9" t="inlineStr">
+      <c r="M114" s="11" t="inlineStr">
         <is>
           <t>(전일) (식품소비재): 배당 2% 인상·실적 호조 흐름 지속, 방어주 선호</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12437,10 +12683,10 @@
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" s="9" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12490,10 +12736,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M116" s="9" t="inlineStr"/>
+      <c r="M116" s="11" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12539,10 +12785,10 @@
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" s="9" t="inlineStr"/>
+      <c r="M117" s="11" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12592,14 +12838,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M118" s="9" t="inlineStr">
+      <c r="M118" s="11" t="inlineStr">
         <is>
           <t>(전일) (캐주얼다이닝): 다수 증권사 목표가 상향(웰스파고 $220)·소고기값 완화 기대</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12645,10 +12891,10 @@
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" s="9" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12694,10 +12940,10 @@
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" s="9" t="inlineStr"/>
+      <c r="M120" s="11" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12743,10 +12989,10 @@
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
-      <c r="M121" s="9" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12796,14 +13042,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M122" s="9" t="inlineStr">
+      <c r="M122" s="11" t="inlineStr">
         <is>
           <t>(전일) (임상시험 CRO): 2Q26 매출 $43.7억(+8.7%)·조정EPS $3.15 비트, 연간 가이던스 상향으로 급등</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12853,10 +13099,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M123" s="9" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12902,10 +13148,10 @@
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" s="9" t="inlineStr"/>
+      <c r="M124" s="11" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12955,10 +13201,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M125" s="9" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13006,10 +13252,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M126" s="9" t="inlineStr"/>
+      <c r="M126" s="11" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+      <c r="A127" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13055,10 +13301,10 @@
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" s="9" t="inlineStr"/>
+      <c r="M127" s="11" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13108,10 +13354,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M128" s="9" t="inlineStr"/>
+      <c r="M128" s="11" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13161,10 +13407,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M129" s="9" t="inlineStr"/>
+      <c r="M129" s="11" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13210,10 +13456,10 @@
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
-      <c r="M130" s="9" t="inlineStr"/>
+      <c r="M130" s="11" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="inlineStr">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13259,10 +13505,10 @@
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
-      <c r="M131" s="9" t="inlineStr"/>
+      <c r="M131" s="11" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13312,10 +13558,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M132" s="9" t="inlineStr"/>
+      <c r="M132" s="11" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
+      <c r="A133" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13359,10 +13605,10 @@
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
-      <c r="M133" s="9" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13408,10 +13654,10 @@
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" s="9" t="inlineStr"/>
+      <c r="M134" s="11" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
+      <c r="A135" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13455,10 +13701,10 @@
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" s="9" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13508,10 +13754,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M136" s="9" t="inlineStr"/>
+      <c r="M136" s="11" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13557,14 +13803,14 @@
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" s="9" t="inlineStr">
+      <c r="M137" s="11" t="inlineStr">
         <is>
           <t>(전일) (결제솔루션): 모건스탠리 업그레이드 이후 연속 강세 지속</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="inlineStr">
+      <c r="A138" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13614,10 +13860,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M138" s="9" t="inlineStr"/>
+      <c r="M138" s="11" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13661,10 +13907,10 @@
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" s="9" t="inlineStr"/>
+      <c r="M139" s="11" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="A140" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13710,10 +13956,10 @@
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" s="9" t="inlineStr"/>
+      <c r="M140" s="11" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13763,10 +14009,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M141" s="9" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="A142" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13812,10 +14058,10 @@
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
-      <c r="M142" s="9" t="inlineStr"/>
+      <c r="M142" s="11" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13865,10 +14111,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M143" s="9" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13914,10 +14160,10 @@
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
-      <c r="M144" s="9" t="inlineStr"/>
+      <c r="M144" s="11" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13963,10 +14209,10 @@
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
-      <c r="M145" s="9" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14014,10 +14260,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M146" s="9" t="inlineStr"/>
+      <c r="M146" s="11" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="inlineStr">
+      <c r="A147" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14067,10 +14313,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M147" s="9" t="inlineStr"/>
+      <c r="M147" s="11" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="inlineStr">
+      <c r="A148" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14120,10 +14366,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M148" s="9" t="inlineStr"/>
+      <c r="M148" s="11" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+      <c r="A149" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14167,14 +14413,14 @@
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" s="9" t="inlineStr">
+      <c r="M149" s="11" t="inlineStr">
         <is>
           <t>(전일) (금융소프트웨어): 2Q 조정EPS $1.76 사상최대, 유기성장 7.6%·가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14220,10 +14466,10 @@
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" s="9" t="inlineStr"/>
+      <c r="M150" s="11" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
+      <c r="A151" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14273,10 +14519,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M151" s="9" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14320,10 +14566,10 @@
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
-      <c r="M152" s="9" t="inlineStr"/>
+      <c r="M152" s="11" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14367,10 +14613,10 @@
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" s="9" t="inlineStr"/>
+      <c r="M153" s="11" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14420,10 +14666,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M154" s="9" t="inlineStr"/>
+      <c r="M154" s="11" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="inlineStr">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14467,10 +14713,10 @@
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" s="9" t="inlineStr"/>
+      <c r="M155" s="11" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="inlineStr">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14520,10 +14766,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M156" s="9" t="inlineStr"/>
+      <c r="M156" s="11" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="inlineStr">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14573,10 +14819,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M157" s="9" t="inlineStr"/>
+      <c r="M157" s="11" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
+      <c r="A158" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14626,10 +14872,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M158" s="9" t="inlineStr"/>
+      <c r="M158" s="11" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
+      <c r="A159" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14679,10 +14925,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M159" s="9" t="inlineStr"/>
+      <c r="M159" s="11" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14728,10 +14974,10 @@
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" s="9" t="inlineStr"/>
+      <c r="M160" s="11" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
+      <c r="A161" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14777,10 +15023,10 @@
         </is>
       </c>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" s="9" t="inlineStr"/>
+      <c r="M161" s="11" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="inlineStr">
+      <c r="A162" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14828,10 +15074,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M162" s="9" t="inlineStr"/>
+      <c r="M162" s="11" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="inlineStr">
+      <c r="A163" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14877,10 +15123,10 @@
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
-      <c r="M163" s="9" t="inlineStr"/>
+      <c r="M163" s="11" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="inlineStr">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14924,10 +15170,10 @@
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" s="9" t="inlineStr"/>
+      <c r="M164" s="11" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="inlineStr">
+      <c r="A165" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14973,10 +15219,10 @@
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" s="9" t="inlineStr"/>
+      <c r="M165" s="11" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="inlineStr">
+      <c r="A166" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15026,10 +15272,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M166" s="9" t="inlineStr"/>
+      <c r="M166" s="11" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="inlineStr">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15079,10 +15325,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M167" s="9" t="inlineStr"/>
+      <c r="M167" s="11" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="inlineStr">
+      <c r="A168" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15128,10 +15374,10 @@
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" s="9" t="inlineStr"/>
+      <c r="M168" s="11" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="inlineStr">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15181,10 +15427,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M169" s="9" t="inlineStr"/>
+      <c r="M169" s="11" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="inlineStr">
+      <c r="A170" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15228,10 +15474,10 @@
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
-      <c r="M170" s="9" t="inlineStr"/>
+      <c r="M170" s="11" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="A171" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15279,10 +15525,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M171" s="9" t="inlineStr"/>
+      <c r="M171" s="11" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="inlineStr">
+      <c r="A172" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15332,10 +15578,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M172" s="9" t="inlineStr"/>
+      <c r="M172" s="11" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="inlineStr">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15381,10 +15627,10 @@
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
-      <c r="M173" s="9" t="inlineStr"/>
+      <c r="M173" s="11" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="inlineStr">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15434,10 +15680,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M174" s="9" t="inlineStr"/>
+      <c r="M174" s="11" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15487,10 +15733,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M175" s="9" t="inlineStr"/>
+      <c r="M175" s="11" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
+      <c r="A176" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15536,10 +15782,10 @@
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" s="9" t="inlineStr"/>
+      <c r="M176" s="11" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
+      <c r="A177" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15589,10 +15835,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M177" s="9" t="inlineStr"/>
+      <c r="M177" s="11" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="inlineStr">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15642,10 +15888,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M178" s="9" t="inlineStr"/>
+      <c r="M178" s="11" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
+      <c r="A179" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15691,10 +15937,10 @@
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
-      <c r="M179" s="9" t="inlineStr"/>
+      <c r="M179" s="11" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="inlineStr">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15744,10 +15990,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M180" s="9" t="inlineStr"/>
+      <c r="M180" s="11" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="inlineStr">
+      <c r="A181" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15793,14 +16039,14 @@
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
-      <c r="M181" s="9" t="inlineStr">
+      <c r="M181" s="11" t="inlineStr">
         <is>
           <t>(전일) (산업용 바코드·모바일컴퓨터): 소프트웨어·AI분석 수요 회복 기대, 목표가 연속 상향으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15850,10 +16096,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M182" s="9" t="inlineStr"/>
+      <c r="M182" s="11" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="inlineStr">
+      <c r="A183" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15899,10 +16145,10 @@
         </is>
       </c>
       <c r="L183" t="inlineStr"/>
-      <c r="M183" s="9" t="inlineStr"/>
+      <c r="M183" s="11" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="A184" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15952,10 +16198,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M184" s="9" t="inlineStr"/>
+      <c r="M184" s="11" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16001,10 +16247,10 @@
         </is>
       </c>
       <c r="L185" t="inlineStr"/>
-      <c r="M185" s="9" t="inlineStr"/>
+      <c r="M185" s="11" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
+      <c r="A186" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16054,14 +16300,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M186" s="9" t="inlineStr">
+      <c r="M186" s="11" t="inlineStr">
         <is>
           <t>(전일) (완성차): 2Q EPS $3.57 예상 상회·연간 가이던스 상향, EV 손실 축소</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="inlineStr">
+      <c r="A187" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16111,10 +16357,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M187" s="9" t="inlineStr"/>
+      <c r="M187" s="11" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
+      <c r="A188" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16160,10 +16406,10 @@
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
-      <c r="M188" s="9" t="inlineStr"/>
+      <c r="M188" s="11" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
+      <c r="A189" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16213,10 +16459,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M189" s="9" t="inlineStr"/>
+      <c r="M189" s="11" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="inlineStr">
+      <c r="A190" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16262,10 +16508,10 @@
         </is>
       </c>
       <c r="L190" t="inlineStr"/>
-      <c r="M190" s="9" t="inlineStr"/>
+      <c r="M190" s="11" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="inlineStr">
+      <c r="A191" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16309,10 +16555,10 @@
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
-      <c r="M191" s="9" t="inlineStr"/>
+      <c r="M191" s="11" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="inlineStr">
+      <c r="A192" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16362,10 +16608,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M192" s="9" t="inlineStr"/>
+      <c r="M192" s="11" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="inlineStr">
+      <c r="A193" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16415,10 +16661,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M193" s="9" t="inlineStr"/>
+      <c r="M193" s="11" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="inlineStr">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16468,7 +16714,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M194" s="9" t="inlineStr">
+      <c r="M194" s="11" t="inlineStr">
         <is>
           <t>(전일) (철도·화물 운송장비): Q2 매출 $31.8억(+17.5%)·EPS $2.76 상회, 수주잔고 $309억(+41.7%)에 가이던스 상향</t>
         </is>
@@ -16572,12 +16818,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16618,15 +16864,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>코쿠사이일렉트릭(반도체 성막장비): SK하이닉스 실적 예상미달+피치 AI투자 리스크경고로 장비주 급락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16667,15 +16917,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>이비덴(ABF기판·IC패키지): SK하이닉스 실적실망+피치 AI투자 리스크경고, 반도체관련주 매도 확대</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16714,15 +16968,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>르네사스(차재·산업용 반도체): SK하이닉스 실적 하회+한국 코스피 급락 여파로 반도체주 전면 하락</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16763,15 +17021,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>레이저테크(EUV 마스크검사장비): SK하이닉스 실적 미달+한국증시 서킷브레이커로 장비주 집중매도</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16812,15 +17074,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>후지쿠라(AI데이터센터 광케이블): 피치 AI대규모투자 신용리스크 경고+반도체관련주 매도 물결</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16861,15 +17127,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16910,15 +17176,15 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16959,15 +17225,15 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17008,15 +17274,15 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17057,15 +17323,15 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17106,15 +17372,15 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17155,15 +17421,15 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17204,15 +17470,15 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17253,10 +17519,10 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17302,14 +17568,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>(전일) (후루카와전공·광섬유): AI광섬유 테마 과열 조정+닛케이 -2566엔 급락 동반 매도로 신저가</t>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>후루카와전기(광섬유·파워케이블): 피치 AI투자 리스크경고 여파, AI테마 고PER주 수급악화로 급락</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17355,14 +17621,14 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>(전일) (디스코·반도체 다이싱장비): 7-9월 순이익 가이던스 395억엔이 컨센 473억엔 대폭 하회로 -12% 급락</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17408,14 +17674,14 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>(전일) (실리콘·PVC): FY27 영업익 계획 5250억엔, 예상 5594억엔 하회 실망 매도</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17461,14 +17727,14 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>(전일) (다이후쿠·반도체팹 자동화): AI투자 둔화 우려로 반도체 자동화장비 섹터 급락 수급으로 신저가</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17514,14 +17780,14 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>(전일) (레조낙·반도체소재): 중국 노광장비 자체제조 보도·아시아 AI반도체 전반 급락 수급으로 신저가</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17567,15 +17833,15 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17616,15 +17882,19 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>코나미그룹(게임·헬스클럽 복합): 카프콤 1Q 영업익 +67% 호실적에 게임주 전반 동반매수</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17669,15 +17939,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>시마노(자전거 부품·낚시): 2Q 순익 +606% 급증 호실적에 상반기 업적 상방수정</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17718,15 +17992,19 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>코마츠(건설기계): 1Q 세전이익 +6.7%, 통기 세전이익 9% 상방수정 발표</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17767,15 +18045,19 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>토요타자동차(자동차): AI·반도체주 급락 속 저PBR 가치주로 자금유입, 엔저 업적개선 기대</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17816,15 +18098,19 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>스바루(자동차): AI반도체 섹터 급락에 저배당·저PBR 자동차주로 자금이동</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17865,15 +18151,15 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17914,15 +18200,15 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17963,15 +18249,15 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18012,15 +18298,15 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18061,15 +18347,15 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18108,15 +18394,15 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18161,15 +18447,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18210,15 +18496,15 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="9" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18259,15 +18545,15 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18308,15 +18594,15 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18361,15 +18647,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18410,15 +18696,15 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18459,15 +18745,15 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18512,15 +18798,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18561,15 +18847,15 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18614,15 +18900,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M42" s="9" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18661,10 +18947,10 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18714,14 +19000,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M44" s="9" t="inlineStr">
+      <c r="M44" s="11" t="inlineStr">
         <is>
           <t>(전일) (브리지스톤·타이어): 1Q 경상이익 +47% 호조, 8/7 결산 기대 매수로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18767,14 +19053,14 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="M45" s="11" t="inlineStr">
         <is>
           <t>(전일) (자동차부품 1위): 7/31 결산 앞둔 기대매수, 日증시 반등 수혜</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18820,14 +19106,14 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr">
+      <c r="M46" s="11" t="inlineStr">
         <is>
           <t>(전일) (게임·완구): 맥쿼리 목표주가 5500→5600엔 상향, 8/5 결산 기대매수</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18871,10 +19157,10 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18920,10 +19206,10 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18973,10 +19259,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M49" s="9" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19022,14 +19308,14 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr">
+      <c r="M50" s="11" t="inlineStr">
         <is>
           <t>(전일) (돈키호테 운영사): 3Q 누적 경상이익 +11.7%, 내수 소매 방어주 수급 유입으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19075,14 +19361,14 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="9" t="inlineStr">
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>(전일) (도쿄디즈니리조트): 입장권 상한 인상 보도·7/30 결산 기대로 연속 급등</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19128,14 +19414,14 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr">
+      <c r="M52" s="11" t="inlineStr">
         <is>
           <t>(전일) (ERP·업무SW): 4-6월 순이익 16%↑ 결산 재평가, IT섹터로 자금 이동</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19185,10 +19471,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M53" s="9" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19234,10 +19520,10 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="9" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19287,10 +19573,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M55" s="9" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19336,10 +19622,10 @@
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" s="9" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19385,14 +19671,14 @@
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="9" t="inlineStr">
+      <c r="M57" s="11" t="inlineStr">
         <is>
           <t>(전일) (아사히맥주): FY26 최종이익 +60% 2기만의 사상최고익 전망·증배로 신고가</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19438,10 +19724,10 @@
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="9" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19487,14 +19773,14 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="9" t="inlineStr">
+      <c r="M59" s="11" t="inlineStr">
         <is>
           <t>(전일) 닛폰스틸(일본 최대 철강): US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19540,10 +19826,10 @@
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="9" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19589,10 +19875,10 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19638,10 +19924,10 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" s="9" t="inlineStr"/>
+      <c r="M62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19687,14 +19973,14 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr">
+      <c r="M63" s="11" t="inlineStr">
         <is>
           <t>(전일) (세븐일레븐 모회사): 1Q 경상이익 +89% 서프라이즈·통기 6.3% 상방수정으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19740,10 +20026,10 @@
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" s="9" t="inlineStr"/>
+      <c r="M64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19789,14 +20075,14 @@
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="9" t="inlineStr">
+      <c r="M65" s="11" t="inlineStr">
         <is>
           <t>(전일) (IT컨설팅·NRI): 7/30 결산 앞두고 기대 매수, FY27 이익 전망 개선으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19846,10 +20132,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M66" s="9" t="inlineStr"/>
+      <c r="M66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19899,10 +20185,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M67" s="9" t="inlineStr"/>
+      <c r="M67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -19946,7 +20232,7 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr"/>
+      <c r="M68" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M68"/>
@@ -20046,12 +20332,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20092,15 +20378,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>몽타주테크(메모리인터페이스칩): AI하드웨어 체인 전반 조정+한국 가격담합 조사 여파, 메모리 섹터 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20141,10 +20431,14 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>SMIC(반도체 파운드리): AI하드웨어 체인 조정 지속, 반도체 섹터 전반 하락에 동반</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20192,14 +20486,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>(전일) (스마트제조 자동화): PCB·AI하드웨어 섹터 급락 연동, 단일 촉매 미확인 동반 급락</t>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>딩타이가오커(PCB 드릴비트 글로벌 1위): AI서버 PCB 섹터 전반 급락(광허테크 등 -16%)에 동반</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20247,14 +20541,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>(전일) (고다층 PCB·성훙커지): 엔비디아 AI서버랙 핵심 PCB 공급, 양산 연기 직격으로 -15% 폭락</t>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>성훙테크H(AI서버 PCB): AI하드웨어 PCB 섹터 조정 지속·엔비디아 루빈 품질 루머 및 이익 정점 우려</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20300,14 +20594,14 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>(전일) (동박적층판 PCB소재·젠타오): 엔비디아 차세대 AI서버랙 PCB 양산 2028년 연기 충격으로 -16% 급락</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20353,14 +20647,14 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>(전일) (광섬유 제조·창페이광섬유): 제프리스 '이익 정점' 경고·증설 공급과잉 전망으로 급락</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20406,14 +20700,14 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>(전일) (낸드 컨트롤러·자오이촹신): 장신메모리 커촹반 상장 첫날 +465%, 그림자주 차익 매도로 -17% 폭락</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20463,19 +20757,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>(전일) (PCB 드릴링 장비·다쭈수콩): 엔비디아 AI서버랙 연기발 하드웨어 설비 수요 우려 약세 지속</t>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>한스CNC(CNC 공작기계): 특별한 뉴스 없음(AI하드웨어·PCB 연관 제조장비 섹터 하락 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20516,15 +20810,19 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>텐센트뮤직(온라인음악 스트리밍): 항셍테크 +2.84%, 텐센트·비리비리 등 대형 인터넷주 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20569,15 +20867,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>스탠다드차타드(국제상업은행): 상반기 세전이익 48억달러(+9%)·2Q 이익 예상 17% 상회·골드만 목표가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20618,15 +20920,19 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>하이얼스마트홈(가전 제조): 신소비·대형소비주 섹터 수급 유입 동반 강세(개별 촉매 미확인, 수급 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20671,15 +20977,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>스와이어퍼시픽B(항공·부동산·음료 복합): 특별한 뉴스 없음(시장 전반 상승 흐름 동반 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20720,15 +21030,19 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>은하오락(마카오 카지노): 마카오 GGR 회복 기대·7월 일평균 매출 전주比 +9%·골드만 매수 유지</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20769,15 +21083,15 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20818,15 +21132,15 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20871,15 +21185,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20920,15 +21234,15 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="M18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20973,10 +21287,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21022,14 +21336,14 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>(전일) (손해보험·중국재보험): 배당지급일 직전 막차 매수 집중, 은행·보험 방어섹터 동반 강세로 신고가</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21073,14 +21387,14 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M21" s="11" t="inlineStr">
         <is>
           <t>(전일) (음식배달·로컬커머스): 미이란 긴장 완화 리스크오프 해소·과기주 매수, 2Q 적자축소 기대</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21130,14 +21444,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>(전일) (가전·로봇): 자사주 매입 집행·휴머노이드 상업화 기대 매수세 유입으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21187,10 +21501,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21236,14 +21550,14 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
         <is>
           <t>(전일) (컨테이너 해운 OOCL): 운임(SCFI) 10주 연속 상승·항로 불안 해소로 운임 강세</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21293,14 +21607,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="M25" s="11" t="inlineStr">
         <is>
           <t>(전일) (국유 대형은행): 독립 촉매 없이 은행 섹터 전반 강세·위안화 강세 수급으로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21350,14 +21664,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="M26" s="11" t="inlineStr">
         <is>
           <t>(전일) (복합기업·부동산): UBS 목표가 20% 상향, 태고지산·캐세이퍼시픽 이익 기여 기대로 신고가</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21403,14 +21717,14 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="M27" s="11" t="inlineStr">
         <is>
           <t>(전일) (국제택배·물류): 자사주 매입 지속, 동남아 패키지 처리량 +84% 역대 최대로 신고가</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21460,10 +21774,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21513,10 +21827,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21566,10 +21880,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21619,14 +21933,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="M31" s="11" t="inlineStr">
         <is>
           <t>(전일) (홍콩 국적 항공사): 캐세이퍼시픽, 상반기 순이익 60~65억 홍콩달러(전년비 최대 +76%) 예고, 여객·화물 호조</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21676,10 +21990,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>HKT트러스트(홍콩 통신): 7/30 중간 실적발표 앞두고 기대 매수 유입(+0.08% 소폭)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -21725,7 +22043,7 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="M33" s="11" t="inlineStr">
         <is>
           <t>(전일) (컨테이너 해운): 상하이운임 10주 연속 상승, 홍해 우회 공급긴축·수출 피크시즌 조기 점화</t>
         </is>
@@ -21829,12 +22147,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -21875,15 +22193,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>메그미터(전력전자 파워서플라이): 홍콩 H주 상장신청에 따른 지분희석 우려+2025 순이익 -66.6% 실적악화 급락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -21924,15 +22246,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>중차이커지(유리섬유·AI전자포): 유상증자(44.8억위안) 희석 우려+AI하드웨어 조정 지속, 과창50 -4% 여파 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -21971,15 +22297,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>신위안(반도체 칩IP설계): 과창50 -4~5% 급락(미 필라델피아반도체 -4.49%·AI과잉투자 우려)+국가IC기금 감산공시 악재</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22020,15 +22350,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>둥산징미(PCB·광모듈): CPO·1.6T 광모듈 가격급락 루머+회사 단가하락 발언, CPO/PCB 연속 하한가권</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22069,15 +22403,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>성훙커지A(PCB): 둥산징미 등 CPO 섹터 연속 급락 여파로 PCB 개념주 동반 하락, 섹터 수급 이탈</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22118,15 +22456,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22165,15 +22503,15 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22214,15 +22552,15 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22263,15 +22601,15 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22312,15 +22650,15 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22361,15 +22699,15 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22410,15 +22748,15 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22459,15 +22797,15 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22508,15 +22846,15 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22561,15 +22899,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22610,15 +22948,15 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22659,15 +22997,15 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="M18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -22708,10 +23046,10 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -22757,14 +23095,14 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>(전일) (광섬유 제조·창페이광섬유): 6월 고점 이후 광통신 섹터 조정 지속, 신규 촉매 없이 약세 연장</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -22808,14 +23146,14 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M21" s="11" t="inlineStr">
         <is>
           <t>(전일) (낸드 스토리지·더밍리): 2분기 순이익 전분기 감소 공시 후 12거래일 7차 하한가, 사이클 전환 공포</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -22863,14 +23201,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>(전일) (우주·특수전원): 상장 초 급등 후 조정 지속, 신규 재료 없음(IPO 거품 해소)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -22916,14 +23254,14 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="M23" s="11" t="inlineStr">
         <is>
           <t>(전일) (광섬유 광케이블·헝퉁광전): AI 연산 수요 불확실·한국 광통신주 동반 하락으로 급락</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -22969,14 +23307,14 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
         <is>
           <t>(전일) (플래시 스토리지·장보룽): 2분기 순이익 전분기 감소, 저장 사이클 정점 우려로 연속 하한가</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -23020,14 +23358,14 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="M25" s="11" t="inlineStr">
         <is>
           <t>(전일) (국산 GPU·무어스레드): AI 하드웨어 섹터 전반 폭락 속 고평가 국산 GPU주 동반 급락</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -23073,14 +23411,14 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="M26" s="11" t="inlineStr">
         <is>
           <t>(전일) (광모듈 CPO·톈푸통신): 장보룽 IPO 충격·한국 반도체 급락 연쇄로 광통신 섹터 -13% 폭락</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -23126,14 +23464,14 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="M27" s="11" t="inlineStr">
         <is>
           <t>(전일) (낸드·디램 모듈·바이웨이추팡): 장보룽 IPO·한국 코스피 서킷브레이커발 저장칩 섹터 급락 연루</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -23179,19 +23517,19 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="M28" s="11" t="inlineStr">
         <is>
           <t>(전일) (PCB·성이전자): 시장 기술주 폭락 속 PCB 섹터 집단 하한가 근접 급락</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -23232,15 +23570,19 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>중궈중처(철도차량 제조): 2Q 신규수주 516억위안(2025매출 18.9%) 모멘텀 지속, 대소비재 강세 속 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -23281,15 +23623,19 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>거리전기(에어컨 제조): AI·반도체주 급락 속 대소비재 역방향 강세, 이구환신(가전 교체보조) 확대 기대</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -23330,15 +23676,19 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>화샤은행(시중은행): 7월 은행섹터 +10% 고배당 로테이션 지속, AI·성장주 급락 속 안전자산 수요로 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -23383,15 +23733,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>젠서은행(국유 대형은행): 7/28 A주 역대 신고가·600억 2차자본채 발행 후 고배당 수급 지속, 신고가 보합</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -23430,15 +23784,19 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>농업은행(국유 대형은행): 섹터 선두 강세 후 신고가권 유지, 월간 고배당·저PB 리레이팅 수급 유입</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -23483,15 +23841,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -23532,10 +23890,10 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -23581,14 +23939,14 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="M36" s="11" t="inlineStr">
         <is>
           <t>(전일) (가전 대형주·하이얼스마트홈): 이구환신 정책 수혜·기술주 급락 반사 방어주 순환매로 신고가</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -23638,14 +23996,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="M37" s="11" t="inlineStr">
         <is>
           <t>(전일) (가전 대표주·메이디그룹): 이구환신 수혜 기대·기술섹터 폭락 반사 순환매로 신고가</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -23691,10 +24049,10 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -23740,14 +24098,14 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr">
+      <c r="M39" s="11" t="inlineStr">
         <is>
           <t>(전일) (우량 주식은행·자오상은행): 기술주 대피 자금이 고배당 은행주로 이동, 배당 매력에 신고가</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -23791,7 +24149,7 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="M40" s="11" t="inlineStr">
         <is>
           <t>(전일) (국유 대형은행): 창업판 급락 속 방어주 순환매로 은행섹터 강세, 공상은행 52주 신고가</t>
         </is>
